--- a/参考資料/履歴書_2409406_岡松礼恩.xlsx
+++ b/参考資料/履歴書_2409406_岡松礼恩.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409406\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2409406\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22747A2-473D-4C7A-AA15-8107BE213398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A2FDEF-D05B-4FAA-AF3D-B00535AA0E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,15 +32,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="89">
   <si>
     <t>履　歴　書</t>
     <rPh sb="0" eb="1">
@@ -618,22 +615,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>私は専門学校のオープンキャンパスに学生スタッフとして参加していました。</t>
-    <rPh sb="0" eb="1">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>センモンガッコウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ガクセイ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>サンカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ゲーム制作演習</t>
     <rPh sb="3" eb="7">
       <t>セイサクエンシュウ</t>
@@ -648,28 +629,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>学業では特に、ゲームの製作に力を入れていました。授業中での</t>
-    <rPh sb="0" eb="2">
-      <t>ガクギョウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>トク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>チカラ</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>イ</t>
-    </rPh>
-    <rPh sb="24" eb="27">
-      <t>ジュギョウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>私は読書が趣味で、小学生のころから漫画や小説、図鑑や専門書など、ジャンルを問わずに様々な本を読</t>
     <rPh sb="0" eb="1">
       <t>ワタシ</t>
@@ -710,160 +669,503 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>んでいます。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>私は情報の整理が得意です。</t>
-    <rPh sb="0" eb="1">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>セイリ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>トクイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>私は、人にプログラムを教えたり、ゲームの制作が楽になるプログラムを書くことが好きです。貴社では主に</t>
-    <rPh sb="0" eb="1">
-      <t>ワタシ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヒト</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オシ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>ラク</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="38" eb="39">
-      <t>ス</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>キシャ</t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t>オモ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>集英社IPを使った版権ゲームの制作以外にも、自社IPのゲームの制作など多くのプロジェクトに参加できる</t>
-    <rPh sb="0" eb="3">
-      <t>シュウエイシャ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ハンケン</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>イガイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ジシャ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>オオ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>サンカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>と考えています。そうした様々なプロジェクトの中で技術や言語、エンジンへの理解を深め、最終的には後輩</t>
-    <rPh sb="1" eb="2">
-      <t>カンガ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サマザマ</t>
-    </rPh>
-    <rPh sb="22" eb="23">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ギジュツ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ゲンゴ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>リカイ</t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t>フカ</t>
-    </rPh>
-    <rPh sb="42" eb="45">
-      <t>サイシュウテキ</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>コウハイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>やチームのメンバーに技術を教えられる立場になりたいです。また、ライブラリやサポートツールの制作を</t>
-    <rPh sb="10" eb="12">
-      <t>ギジュツ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>オシ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>タチバ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>セイサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>行うチームに入り、制作したライブラリやツールでプロジェクト全体の作業を円滑にしていきたいです。</t>
-    <rPh sb="0" eb="1">
-      <t>オコナ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ハイ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>セイサク</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>サギョウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>エンカツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>以上</t>
     <rPh sb="0" eb="2">
       <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>貴社では集英社IPを使った版権ゲームの制作を行っており、原作の魅力を十分にゲームとして</t>
+    <rPh sb="0" eb="2">
+      <t>キシャ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>シュウエイシャ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ハンケン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ゲンサク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ミリョク</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ジュウブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表現できている点で他社には真似ができないと感じましたので、志望しました。特に、原作の</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウゲン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>タシャ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>マネ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シボウ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ゲンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>創作に関わり、将来的には後輩やチームメンバーに技術を教えられる人材を目指します。</t>
+    <rPh sb="0" eb="2">
+      <t>ソウサク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カカ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>ショウライテキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>コウハイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ギジュツ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>オシ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ジンザイ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>メザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雰囲気を再現したエフェクトやモーションなどが魅力的で、プログラマーとしてゲームが最もよい</t>
+    <rPh sb="0" eb="3">
+      <t>フンイキ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>サイゲン</t>
+    </rPh>
+    <rPh sb="22" eb="25">
+      <t>ミリョクテキ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>モット</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>形になるように関りたいと考えています。また、貴社の自社IPなどの魅力的なIPコンテンツの</t>
+    <rPh sb="0" eb="1">
+      <t>カタチ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カカ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>キシャ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ジシャ</t>
+    </rPh>
+    <rPh sb="32" eb="35">
+      <t>ミリョクテキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は情報の整理が得意です。人から聞いた情報を整理し、別の人に伝達したり、質問の内容を</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トクイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>デンタツ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>整理してより正確に答えることができます。授業でのチーム制作の際、レベルデザインの担当で</t>
+    <rPh sb="0" eb="2">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セイカク</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ジュギョウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>サイ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あったチームメンバーがステージをなかなか完成させられず、制作が停滞していました。そこで、</t>
+    <rPh sb="20" eb="22">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>テイタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒアリングを行ったところ、ゲームのロジックが理解できていないことが原因であるとわかりました。</t>
+    <rPh sb="6" eb="7">
+      <t>オコナ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>リカイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ゲンイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ヒアリングの内容からゲームのロジックの情報を整理し直し、チームメンバーに伝えたところ、</t>
+    <rPh sb="6" eb="8">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無事にステージが完成し、制作が進行しました。この経験を入社後もチームの中で生かしたいです。</t>
+    <rPh sb="0" eb="2">
+      <t>ブジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シンコウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ケイケン</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>ニュウシャゴ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>時間を活用し、作品の制作に打ち込みました。また、自身の作品の制作だけではなくクラスメイト</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>の作品の制作に、アドバイスを出したり、わからない点や質問に対して答えることもありました。</t>
+    <rPh sb="1" eb="3">
+      <t>サクヒン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ダ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>テン</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>コタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学業では特に、ゲームの制作に力を入れていました。授業中での作業だけではなく、放課後の</t>
+    <rPh sb="0" eb="2">
+      <t>ガクギョウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セイサク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>チカラ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="24" eb="27">
+      <t>ジュギョウチュウ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="38" eb="41">
+      <t>ホウカゴ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入社後もこの姿勢のまま、与えられた仕事に熱意をもって取り組んでいきたいと考えています。</t>
+    <rPh sb="0" eb="3">
+      <t>ニュウシャゴ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>シセイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>アタ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シゴト</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ネツイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カンガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>んでいます。中でも歴史学についての本や歴史小説が好きで、最近読んだ本の中で、「万物の黎明」</t>
+    <rPh sb="6" eb="7">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>レキシガク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>レキシ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ショウセツ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ス</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>サイキン</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>バンブツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>の補助以外にも、高校生の方々の質問に答えたり、進路についての相談を受けることもありました。</t>
+    <rPh sb="1" eb="3">
+      <t>ホジョ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>コウコウセイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カタガタ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>シツモン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>コタ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>シンロ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は専門学校のオープンキャンパスに学生スタッフとして参加していました。体験授業中の先生</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>センモンガッコウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガクセイ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>サンカ</t>
+    </rPh>
+    <rPh sb="35" eb="40">
+      <t>タイケンジュギョウチュウ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>センセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>が最も興味深かったです。</t>
+    <rPh sb="1" eb="2">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キョウミ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ブカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そういった中で、初対面の人とのコミュニケーションを学ぶことができました。</t>
+    <rPh sb="5" eb="6">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>ショタイメン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>マナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1582,13 +1884,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1819,7 +2121,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3746,7 +4048,7 @@
       <c r="G29" s="101"/>
       <c r="H29" s="24"/>
       <c r="I29" s="102" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J29" s="102"/>
       <c r="K29" s="102"/>
@@ -4499,7 +4801,7 @@
     <row r="46" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="4"/>
       <c r="B46" s="70" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C46" s="70"/>
       <c r="D46" s="70"/>
@@ -4545,7 +4847,7 @@
     <row r="47" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="4"/>
       <c r="B47" s="70" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C47" s="70"/>
       <c r="D47" s="70"/>
@@ -4591,7 +4893,7 @@
     <row r="48" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="4"/>
       <c r="B48" s="70" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C48" s="70"/>
       <c r="D48" s="70"/>
@@ -4637,7 +4939,7 @@
     <row r="49" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="4"/>
       <c r="B49" s="70" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C49" s="70"/>
       <c r="D49" s="70"/>
@@ -4683,7 +4985,7 @@
     <row r="50" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="4"/>
       <c r="B50" s="70" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C50" s="70"/>
       <c r="D50" s="70"/>
@@ -4775,7 +5077,7 @@
     <row r="52" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="4"/>
       <c r="B52" s="70" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C52" s="70"/>
       <c r="D52" s="70"/>
@@ -4820,7 +5122,9 @@
     </row>
     <row r="53" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="4"/>
-      <c r="B53" s="70"/>
+      <c r="B53" s="70" t="s">
+        <v>75</v>
+      </c>
       <c r="C53" s="70"/>
       <c r="D53" s="70"/>
       <c r="E53" s="70"/>
@@ -4864,7 +5168,9 @@
     </row>
     <row r="54" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="4"/>
-      <c r="B54" s="70"/>
+      <c r="B54" s="70" t="s">
+        <v>76</v>
+      </c>
       <c r="C54" s="70"/>
       <c r="D54" s="70"/>
       <c r="E54" s="70"/>
@@ -4908,7 +5214,9 @@
     </row>
     <row r="55" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="4"/>
-      <c r="B55" s="70"/>
+      <c r="B55" s="70" t="s">
+        <v>77</v>
+      </c>
       <c r="C55" s="70"/>
       <c r="D55" s="70"/>
       <c r="E55" s="70"/>
@@ -4952,7 +5260,9 @@
     </row>
     <row r="56" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="4"/>
-      <c r="B56" s="70"/>
+      <c r="B56" s="70" t="s">
+        <v>78</v>
+      </c>
       <c r="C56" s="70"/>
       <c r="D56" s="70"/>
       <c r="E56" s="70"/>
@@ -4996,7 +5306,9 @@
     </row>
     <row r="57" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="39"/>
-      <c r="B57" s="124"/>
+      <c r="B57" s="124" t="s">
+        <v>79</v>
+      </c>
       <c r="C57" s="124"/>
       <c r="D57" s="124"/>
       <c r="E57" s="124"/>
@@ -5054,7 +5366,7 @@
       <c r="K58" s="71"/>
       <c r="L58" s="71"/>
       <c r="M58" s="71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N58" s="71"/>
       <c r="O58" s="71"/>
@@ -5089,7 +5401,7 @@
     <row r="59" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="4"/>
       <c r="B59" s="70" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C59" s="70"/>
       <c r="D59" s="70"/>
@@ -5134,7 +5446,9 @@
     </row>
     <row r="60" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="4"/>
-      <c r="B60" s="70"/>
+      <c r="B60" s="70" t="s">
+        <v>80</v>
+      </c>
       <c r="C60" s="70"/>
       <c r="D60" s="70"/>
       <c r="E60" s="70"/>
@@ -5178,7 +5492,9 @@
     </row>
     <row r="61" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="4"/>
-      <c r="B61" s="70"/>
+      <c r="B61" s="70" t="s">
+        <v>81</v>
+      </c>
       <c r="C61" s="70"/>
       <c r="D61" s="70"/>
       <c r="E61" s="70"/>
@@ -5222,7 +5538,9 @@
     </row>
     <row r="62" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="4"/>
-      <c r="B62" s="124"/>
+      <c r="B62" s="124" t="s">
+        <v>83</v>
+      </c>
       <c r="C62" s="124"/>
       <c r="D62" s="124"/>
       <c r="E62" s="124"/>
@@ -5275,7 +5593,7 @@
       <c r="F63" s="71"/>
       <c r="G63" s="71"/>
       <c r="H63" s="71" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I63" s="71"/>
       <c r="J63" s="71"/>
@@ -5315,7 +5633,7 @@
     <row r="64" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="4"/>
       <c r="B64" s="70" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C64" s="70"/>
       <c r="D64" s="70"/>
@@ -5361,7 +5679,7 @@
     <row r="65" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="4"/>
       <c r="B65" s="70" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C65" s="70"/>
       <c r="D65" s="70"/>
@@ -5406,7 +5724,9 @@
     </row>
     <row r="66" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="4"/>
-      <c r="B66" s="70"/>
+      <c r="B66" s="70" t="s">
+        <v>87</v>
+      </c>
       <c r="C66" s="70"/>
       <c r="D66" s="70"/>
       <c r="E66" s="70"/>
@@ -5497,7 +5817,7 @@
     <row r="68" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="4"/>
       <c r="B68" s="70" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C68" s="70"/>
       <c r="D68" s="70"/>
@@ -5542,7 +5862,9 @@
     </row>
     <row r="69" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="4"/>
-      <c r="B69" s="70"/>
+      <c r="B69" s="70" t="s">
+        <v>85</v>
+      </c>
       <c r="C69" s="70"/>
       <c r="D69" s="70"/>
       <c r="E69" s="70"/>
@@ -5586,7 +5908,9 @@
     </row>
     <row r="70" spans="1:42" ht="26.1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="9"/>
-      <c r="B70" s="114"/>
+      <c r="B70" s="114" t="s">
+        <v>88</v>
+      </c>
       <c r="C70" s="114"/>
       <c r="D70" s="114"/>
       <c r="E70" s="114"/>
@@ -5814,15 +6138,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FF5E1D608BDB6F4BB724232E49577B65" ma:contentTypeVersion="0" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="051359e5bb8aa340ac7de897f44180f6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="59eb99ccec9652907e05478db3a26565">
     <xsd:element name="properties">
@@ -5936,21 +6251,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71437A5E-7800-45EA-95D8-242D4908BE87}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{456938A2-5BB7-4697-B0FF-D18487EC1260}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5966,7 +6282,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCA4009D-F4D3-4746-8FA1-9B3FC97437D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -5975,4 +6291,12 @@
     <ds:schemaRef ds:uri="12a8c780-0195-41dc-89a7-44d579d7847b"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71437A5E-7800-45EA-95D8-242D4908BE87}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>